--- a/chapters/12/core/AIHE-D05/supp/AIHE-J/xlsx/AIHE-J_workbook.xlsx
+++ b/chapters/12/core/AIHE-D05/supp/AIHE-J/xlsx/AIHE-J_workbook.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Re149cb1b1c944f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2T1_J_1_AI_lifecycle_ch_Blank" sheetId="2" r:id="R6329f5401852491b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2T1_J_1_AI_lifecycle_ch_Worked" sheetId="3" r:id="R75d16d1c44b645e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3T1_J_2_Model_monitorin_Blank" sheetId="4" r:id="R23f4dbeac1fb47d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3T1_J_2_Model_monitorin_Worked" sheetId="5" r:id="Raf038490de2c403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4T1_J_3_AI_update_and_v_Blank" sheetId="6" r:id="R9a46d1797ac5421d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4T1_J_3_AI_update_and_v_Worked" sheetId="7" r:id="R4bbe82be9d8e482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5T1_J_4_Decommissioning_Blank" sheetId="8" r:id="Re3a0a8428bfd4f60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5T1_J_4_Decommissioning_Worked" sheetId="9" r:id="R193f7374e8284048"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6T1_J_5_Future_proof_pr_Blank" sheetId="10" r:id="R663ed8345bcd425b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6T1_J_5_Future_proof_pr_Worked" sheetId="11" r:id="R6cd2f544f57340f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7T1_J_6_Scenario_planni_Blank" sheetId="12" r:id="Rb040851e763b472b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7T1_J_6_Scenario_planni_Worked" sheetId="13" r:id="R193d613415484917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S8T1_J_7_Annual_policy_a_Blank" sheetId="14" r:id="Rb50657d7363f4847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S8T1_J_7_Annual_policy_a_Worked" sheetId="15" r:id="R649038a11b0c40c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9T1_J_8_Future_proof_AI_Blank" sheetId="16" r:id="Ra96aa0d57ad54e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9T1_J_8_Future_proof_AI_Worked" sheetId="17" r:id="Ra5bd947b3b134c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Re721f114eae14afc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2T1_J_1_AI_lifecycle_ch_Blank" sheetId="2" r:id="Rf67aecd9520a43b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2T1_J_1_AI_lifecycle_ch_Worked" sheetId="3" r:id="Rda3259fea8ef4f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3T1_J_2_Model_monitorin_Blank" sheetId="4" r:id="R597d7955064342af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3T1_J_2_Model_monitorin_Worked" sheetId="5" r:id="Rb57f3f6dbbce4216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4T1_J_3_AI_update_and_v_Blank" sheetId="6" r:id="R0a52c32f57e7498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4T1_J_3_AI_update_and_v_Worked" sheetId="7" r:id="R941d2095f79448fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5T1_J_4_Decommissioning_Blank" sheetId="8" r:id="R4ee5b2c698bd4eae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5T1_J_4_Decommissioning_Worked" sheetId="9" r:id="R6ed55bfbd1924cf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6T1_J_5_Future_proof_pr_Blank" sheetId="10" r:id="R0e0e2c6d13214b44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6T1_J_5_Future_proof_pr_Worked" sheetId="11" r:id="Rdcee69dac0d443cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7T1_J_6_Scenario_planni_Blank" sheetId="12" r:id="Rb3d28e83c71c4c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S7T1_J_6_Scenario_planni_Worked" sheetId="13" r:id="Rae20207054444404"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S8T1_J_7_Annual_policy_a_Blank" sheetId="14" r:id="R4951d215e9f445a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S8T1_J_7_Annual_policy_a_Worked" sheetId="15" r:id="R35cecd5877a244ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9T1_J_8_Future_proof_AI_Blank" sheetId="16" r:id="Rbd5ee356b17b42ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S9T1_J_8_Future_proof_AI_Worked" sheetId="17" r:id="R047a734f7af24fac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -29,7 +29,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -46,8 +46,14 @@
       <x:color rgb="FF17365D"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,6 +80,16 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF303236"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -82,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
@@ -149,6 +165,43 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -380,7 +433,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="9" t="inlineStr">
+      <x:c r="A1" s="45" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Digital Resource AIHE-J: Lifecycle and Future-Proofing Toolkit</x:t>
         </x:is>
@@ -393,7 +446,7 @@
     </x:row>
     <x:row r="2"/>
     <x:row r="3">
-      <x:c r="A3" s="12" t="inlineStr">
+      <x:c r="A3" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Resource ID</x:t>
         </x:is>
@@ -405,19 +458,17 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="12" t="inlineStr">
+      <x:c r="A4" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Version</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">V1.0</x:t>
-        </x:is>
+      <x:c r="B4" s="17" t="str">
+        <x:v>V1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="12" t="inlineStr">
+      <x:c r="A5" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Last reviewed</x:t>
         </x:is>
@@ -429,19 +480,17 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="12" t="inlineStr">
+      <x:c r="A6" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Related chapters</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Chapters 16 and 18</x:t>
-        </x:is>
+      <x:c r="B6" s="17" t="str">
+        <x:v>Chapters </x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12" t="inlineStr">
+      <x:c r="A7" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Intended users</x:t>
         </x:is>
@@ -453,7 +502,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="12" t="inlineStr">
+      <x:c r="A8" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Status</x:t>
         </x:is>
@@ -465,7 +514,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12" t="inlineStr">
+      <x:c r="A9" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Privacy</x:t>
         </x:is>
@@ -477,7 +526,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12" t="inlineStr">
+      <x:c r="A10" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Instructions</x:t>
         </x:is>
@@ -505,12 +554,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Procurement area</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Required question</x:t>
         </x:is>
@@ -522,7 +571,7 @@
           <x:t xml:space="preserve">Evidence</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="inlineStr">
+      <x:c r="B2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What clinical, economic, and real-world evidence supports the product?</x:t>
         </x:is>
@@ -534,7 +583,7 @@
           <x:t xml:space="preserve">Local validation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="inlineStr">
+      <x:c r="B3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Will the vendor support validation using local hospital data?</x:t>
         </x:is>
@@ -546,7 +595,7 @@
           <x:t xml:space="preserve">Interoperability</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="inlineStr">
+      <x:c r="B4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Does the system support open standards and integration with existing infrastructure?</x:t>
         </x:is>
@@ -558,7 +607,7 @@
           <x:t xml:space="preserve">Data ownership</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="inlineStr">
+      <x:c r="B5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Who owns input data, output data, logs, derived data, and model-improvement data?</x:t>
         </x:is>
@@ -570,7 +619,7 @@
           <x:t xml:space="preserve">Audit access</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="inlineStr">
+      <x:c r="B6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Can the hospital audit performance, bias, usage, and safety?</x:t>
         </x:is>
@@ -582,7 +631,7 @@
           <x:t xml:space="preserve">Versioning</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="inlineStr">
+      <x:c r="B7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">How are model updates documented, tested, and approved?</x:t>
         </x:is>
@@ -594,7 +643,7 @@
           <x:t xml:space="preserve">Cybersecurity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="inlineStr">
+      <x:c r="B8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What security certifications, controls, and incident response procedures are in place?</x:t>
         </x:is>
@@ -606,7 +655,7 @@
           <x:t xml:space="preserve">Cost escalation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="30" t="inlineStr">
+      <x:c r="B9" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are future fees, maintenance costs, and integration costs predictable?</x:t>
         </x:is>
@@ -618,7 +667,7 @@
           <x:t xml:space="preserve">Exit strategy</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="inlineStr">
+      <x:c r="B10" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Can the hospital export data and discontinue without vendor lock-in?</x:t>
         </x:is>
@@ -630,7 +679,7 @@
           <x:t xml:space="preserve">Human oversight</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="30" t="inlineStr">
+      <x:c r="B11" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What decisions require human review and accountability?</x:t>
         </x:is>
@@ -650,12 +699,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Procurement area</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Required question</x:t>
         </x:is>
@@ -797,22 +846,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Scenario</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Expected effect on AI adoption</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="24" t="inlineStr">
+      <x:c r="C1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hospital response</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="24" t="inlineStr">
+      <x:c r="D1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Review notes</x:t>
         </x:is>
@@ -824,9 +873,9 @@
           <x:t xml:space="preserve">Stronger regulation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="str"/>
-      <x:c r="C2" s="30" t="str"/>
-      <x:c r="D2" s="30" t="inlineStr">
+      <x:c r="B2" s="48" t="str"/>
+      <x:c r="C2" s="48" t="str"/>
+      <x:c r="D2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What evidence and documentation become more important?</x:t>
         </x:is>
@@ -838,9 +887,9 @@
           <x:t xml:space="preserve">Vendor price escalation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="str"/>
-      <x:c r="C3" s="30" t="str"/>
-      <x:c r="D3" s="30" t="inlineStr">
+      <x:c r="B3" s="48" t="str"/>
+      <x:c r="C3" s="48" t="str"/>
+      <x:c r="D3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">How does this affect budget impact and contract design?</x:t>
         </x:is>
@@ -852,9 +901,9 @@
           <x:t xml:space="preserve">Major cybersecurity incident</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="str"/>
-      <x:c r="C4" s="30" t="str"/>
-      <x:c r="D4" s="30" t="inlineStr">
+      <x:c r="B4" s="48" t="str"/>
+      <x:c r="C4" s="48" t="str"/>
+      <x:c r="D4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What continuity and trust measures are needed?</x:t>
         </x:is>
@@ -866,9 +915,9 @@
           <x:t xml:space="preserve">Rapid improvement in competing tools</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="str"/>
-      <x:c r="C5" s="30" t="str"/>
-      <x:c r="D5" s="30" t="inlineStr">
+      <x:c r="B5" s="48" t="str"/>
+      <x:c r="C5" s="48" t="str"/>
+      <x:c r="D5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">When should the hospital switch or decommission?</x:t>
         </x:is>
@@ -880,9 +929,9 @@
           <x:t xml:space="preserve">Public trust crisis</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="str"/>
-      <x:c r="C6" s="30" t="str"/>
-      <x:c r="D6" s="30" t="inlineStr">
+      <x:c r="B6" s="48" t="str"/>
+      <x:c r="C6" s="48" t="str"/>
+      <x:c r="D6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">How should the hospital communicate and govern AI?</x:t>
         </x:is>
@@ -894,9 +943,9 @@
           <x:t xml:space="preserve">Health data space expansion</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="str"/>
-      <x:c r="C7" s="30" t="str"/>
-      <x:c r="D7" s="30" t="inlineStr">
+      <x:c r="B7" s="48" t="str"/>
+      <x:c r="C7" s="48" t="str"/>
+      <x:c r="D7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">How can secondary use support public value?</x:t>
         </x:is>
@@ -908,9 +957,9 @@
           <x:t xml:space="preserve">Workforce shortage worsens</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="str"/>
-      <x:c r="C8" s="30" t="str"/>
-      <x:c r="D8" s="30" t="inlineStr">
+      <x:c r="B8" s="48" t="str"/>
+      <x:c r="C8" s="48" t="str"/>
+      <x:c r="D8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Which AI use cases become more attractive?</x:t>
         </x:is>
@@ -932,22 +981,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Scenario</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Expected effect on AI adoption</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="24" t="inlineStr">
+      <x:c r="C1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hospital response</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="24" t="inlineStr">
+      <x:c r="D1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Review notes</x:t>
         </x:is>
@@ -1093,12 +1142,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Update item</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Notes for current year</x:t>
         </x:is>
@@ -1110,7 +1159,7 @@
           <x:t xml:space="preserve">Major regulatory changes</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="str"/>
+      <x:c r="B2" s="48" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="inlineStr">
@@ -1118,7 +1167,7 @@
           <x:t xml:space="preserve">Updated evidence standards or reporting guidelines</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="str"/>
+      <x:c r="B3" s="48" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="inlineStr">
@@ -1126,7 +1175,7 @@
           <x:t xml:space="preserve">New AI health economics studies or reviews</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="str"/>
+      <x:c r="B4" s="48" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17" t="inlineStr">
@@ -1134,7 +1183,7 @@
           <x:t xml:space="preserve">New privacy, cybersecurity, or data governance requirements</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="str"/>
+      <x:c r="B5" s="48" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17" t="inlineStr">
@@ -1142,7 +1191,7 @@
           <x:t xml:space="preserve">New examples of generative, multimodal, or agentic AI in healthcare</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="str"/>
+      <x:c r="B6" s="48" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="inlineStr">
@@ -1150,7 +1199,7 @@
           <x:t xml:space="preserve">Important AI failures, recalls, or safety incidents</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="str"/>
+      <x:c r="B7" s="48" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="inlineStr">
@@ -1158,19 +1207,19 @@
           <x:t xml:space="preserve">New reimbursement or procurement developments</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="str"/>
+      <x:c r="B8" s="48" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="str">
         <x:v>Worked examples to replace or revise</x:v>
       </x:c>
-      <x:c r="B9" s="30" t="str"/>
+      <x:c r="B9" s="48" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
         <x:v>Recommended updates to guidance or templates</x:v>
       </x:c>
-      <x:c r="B10" s="30" t="str"/>
+      <x:c r="B10" s="48" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1186,12 +1235,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Update item</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Notes for current year</x:t>
         </x:is>
@@ -1311,12 +1360,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Dossier section</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Required content</x:t>
         </x:is>
@@ -1328,7 +1377,7 @@
           <x:t xml:space="preserve">1. Problem definition</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="inlineStr">
+      <x:c r="B2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hospital problem, affected population, workflow, and current pain points</x:t>
         </x:is>
@@ -1340,7 +1389,7 @@
           <x:t xml:space="preserve">2. AI use case</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="inlineStr">
+      <x:c r="B3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Description of the AI intervention, intended users, and intended decisions</x:t>
         </x:is>
@@ -1352,7 +1401,7 @@
           <x:t xml:space="preserve">3. Comparator</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="inlineStr">
+      <x:c r="B4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Usual care or realistic alternative intervention</x:t>
         </x:is>
@@ -1364,7 +1413,7 @@
           <x:t xml:space="preserve">4. Evidence base</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="inlineStr">
+      <x:c r="B5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Technical, clinical, implementation, and economic evidence</x:t>
         </x:is>
@@ -1376,7 +1425,7 @@
           <x:t xml:space="preserve">5. Data readiness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="inlineStr">
+      <x:c r="B6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Data sources, quality, interoperability, representativeness, legal use</x:t>
         </x:is>
@@ -1388,7 +1437,7 @@
           <x:t xml:space="preserve">6. Economic evaluation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="inlineStr">
+      <x:c r="B7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cost inventory, ROI, CEA, BIA, uncertainty, and sensitivity analysis</x:t>
         </x:is>
@@ -1400,7 +1449,7 @@
           <x:t xml:space="preserve">7. Ethical governance</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="inlineStr">
+      <x:c r="B8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Accountability, transparency, fairness, oversight, consent, public value</x:t>
         </x:is>
@@ -1412,7 +1461,7 @@
           <x:t xml:space="preserve">8. Privacy and cybersecurity</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="30" t="inlineStr">
+      <x:c r="B9" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Data protection, access controls, incident response, continuity plan</x:t>
         </x:is>
@@ -1424,7 +1473,7 @@
           <x:t xml:space="preserve">9. Equity impact</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="inlineStr">
+      <x:c r="B10" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Who may benefit, who may be excluded, subgroup performance, mitigation</x:t>
         </x:is>
@@ -1436,7 +1485,7 @@
           <x:t xml:space="preserve">10. Implementation plan</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="30" t="inlineStr">
+      <x:c r="B11" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Pilot, validation, training, communication, scaling, and monitoring</x:t>
         </x:is>
@@ -1448,7 +1497,7 @@
           <x:t xml:space="preserve">11. Future-proofing plan</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" s="30" t="inlineStr">
+      <x:c r="B12" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Lifecycle monitoring, change control, update criteria, decommissioning triggers</x:t>
         </x:is>
@@ -1460,7 +1509,7 @@
           <x:t xml:space="preserve">12. Final recommendation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" s="30" t="inlineStr">
+      <x:c r="B13" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Adopt, pilot, modify, delay, reject, or decommission</x:t>
         </x:is>
@@ -1480,12 +1529,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Dossier section</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Required content</x:t>
         </x:is>
@@ -1650,17 +1699,17 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Lifecycle domain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Checklist question</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="24" t="inlineStr">
+      <x:c r="C1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Evidence or document</x:t>
         </x:is>
@@ -1672,12 +1721,12 @@
           <x:t xml:space="preserve">Problem definition</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="inlineStr">
+      <x:c r="B2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Is the hospital problem clearly defined, and is AI necessary?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C2" s="30" t="inlineStr">
+      <x:c r="C2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AI Use-Case Canvas</x:t>
         </x:is>
@@ -1689,12 +1738,12 @@
           <x:t xml:space="preserve">Comparator</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="inlineStr">
+      <x:c r="B3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What is the realistic alternative to AI?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" s="30" t="inlineStr">
+      <x:c r="C3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Decision problem template</x:t>
         </x:is>
@@ -1706,12 +1755,12 @@
           <x:t xml:space="preserve">Data readiness</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="inlineStr">
+      <x:c r="B4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are data complete, representative, interoperable, and legally usable?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="30" t="inlineStr">
+      <x:c r="C4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Data readiness report</x:t>
         </x:is>
@@ -1723,12 +1772,12 @@
           <x:t xml:space="preserve">Validation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="inlineStr">
+      <x:c r="B5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Has the model been tested locally and across relevant subgroups?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C5" s="30" t="inlineStr">
+      <x:c r="C5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Validation plan and results</x:t>
         </x:is>
@@ -1740,12 +1789,12 @@
           <x:t xml:space="preserve">Economic evaluation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="inlineStr">
+      <x:c r="B6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are lifecycle costs, benefits, and uncertainty assessed?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="30" t="inlineStr">
+      <x:c r="C6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TCO, ROI, CEA, or BIA worksheet</x:t>
         </x:is>
@@ -1757,12 +1806,12 @@
           <x:t xml:space="preserve">Ethical governance</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="inlineStr">
+      <x:c r="B7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are accountability, fairness, transparency, and human oversight defined?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="30" t="inlineStr">
+      <x:c r="C7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Ethical governance checklist</x:t>
         </x:is>
@@ -1774,12 +1823,12 @@
           <x:t xml:space="preserve">Implementation</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="inlineStr">
+      <x:c r="B8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Is there a staged implementation plan with training and workflow redesign?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="30" t="inlineStr">
+      <x:c r="C8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Implementation roadmap</x:t>
         </x:is>
@@ -1791,12 +1840,12 @@
           <x:t xml:space="preserve">Monitoring</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="30" t="inlineStr">
+      <x:c r="B9" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are performance, cost, equity, workflow, and safety indicators monitored?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="30" t="inlineStr">
+      <x:c r="C9" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Algorithmovigilance dashboard</x:t>
         </x:is>
@@ -1808,12 +1857,12 @@
           <x:t xml:space="preserve">Updating</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="inlineStr">
+      <x:c r="B10" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are model changes documented, validated, and approved?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="30" t="inlineStr">
+      <x:c r="C10" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Change-control log</x:t>
         </x:is>
@@ -1825,12 +1874,12 @@
           <x:t xml:space="preserve">Decommissioning</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="30" t="inlineStr">
+      <x:c r="B11" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Are stopping rules and exit procedures defined?</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="30" t="inlineStr">
+      <x:c r="C11" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Decommissioning checklist</x:t>
         </x:is>
@@ -1851,17 +1900,17 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Lifecycle domain</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Checklist question</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="24" t="inlineStr">
+      <x:c r="C1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Evidence or document</x:t>
         </x:is>
@@ -2055,32 +2104,32 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Indicator</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Baseline value</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="24" t="inlineStr">
+      <x:c r="C1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Current value</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="24" t="inlineStr">
+      <x:c r="D1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Threshold for review</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="24" t="inlineStr">
+      <x:c r="E1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Responsible role</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" s="24" t="inlineStr">
+      <x:c r="F1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Action taken</x:t>
         </x:is>
@@ -2092,15 +2141,15 @@
           <x:t xml:space="preserve">Model discrimination</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="str"/>
-      <x:c r="C2" s="30" t="str"/>
-      <x:c r="D2" s="30" t="str"/>
-      <x:c r="E2" s="30" t="inlineStr">
+      <x:c r="B2" s="48" t="str"/>
+      <x:c r="C2" s="48" t="str"/>
+      <x:c r="D2" s="48" t="str"/>
+      <x:c r="E2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Data science / clinical lead</x:t>
         </x:is>
       </x:c>
-      <x:c r="F2" s="30" t="str"/>
+      <x:c r="F2" s="48" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="inlineStr">
@@ -2108,15 +2157,15 @@
           <x:t xml:space="preserve">Calibration</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="str"/>
-      <x:c r="C3" s="30" t="str"/>
-      <x:c r="D3" s="30" t="str"/>
-      <x:c r="E3" s="30" t="inlineStr">
+      <x:c r="B3" s="48" t="str"/>
+      <x:c r="C3" s="48" t="str"/>
+      <x:c r="D3" s="48" t="str"/>
+      <x:c r="E3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Data science / quality team</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" s="30" t="str"/>
+      <x:c r="F3" s="48" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="inlineStr">
@@ -2124,15 +2173,15 @@
           <x:t xml:space="preserve">False-positive rate</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="str"/>
-      <x:c r="C4" s="30" t="str"/>
-      <x:c r="D4" s="30" t="str"/>
-      <x:c r="E4" s="30" t="inlineStr">
+      <x:c r="B4" s="48" t="str"/>
+      <x:c r="C4" s="48" t="str"/>
+      <x:c r="D4" s="48" t="str"/>
+      <x:c r="E4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Clinical lead</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="30" t="str"/>
+      <x:c r="F4" s="48" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17" t="inlineStr">
@@ -2140,15 +2189,15 @@
           <x:t xml:space="preserve">False-negative rate</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="str"/>
-      <x:c r="C5" s="30" t="str"/>
-      <x:c r="D5" s="30" t="str"/>
-      <x:c r="E5" s="30" t="inlineStr">
+      <x:c r="B5" s="48" t="str"/>
+      <x:c r="C5" s="48" t="str"/>
+      <x:c r="D5" s="48" t="str"/>
+      <x:c r="E5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Clinical safety lead</x:t>
         </x:is>
       </x:c>
-      <x:c r="F5" s="30" t="str"/>
+      <x:c r="F5" s="48" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17" t="inlineStr">
@@ -2156,15 +2205,15 @@
           <x:t xml:space="preserve">Subgroup performance</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="str"/>
-      <x:c r="C6" s="30" t="str"/>
-      <x:c r="D6" s="30" t="str"/>
-      <x:c r="E6" s="30" t="inlineStr">
+      <x:c r="B6" s="48" t="str"/>
+      <x:c r="C6" s="48" t="str"/>
+      <x:c r="D6" s="48" t="str"/>
+      <x:c r="E6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Equity / ethics representative</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="30" t="str"/>
+      <x:c r="F6" s="48" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="inlineStr">
@@ -2172,15 +2221,15 @@
           <x:t xml:space="preserve">Alert volume</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="str"/>
-      <x:c r="C7" s="30" t="str"/>
-      <x:c r="D7" s="30" t="str"/>
-      <x:c r="E7" s="30" t="inlineStr">
+      <x:c r="B7" s="48" t="str"/>
+      <x:c r="C7" s="48" t="str"/>
+      <x:c r="D7" s="48" t="str"/>
+      <x:c r="E7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Workflow lead</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="30" t="str"/>
+      <x:c r="F7" s="48" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="inlineStr">
@@ -2188,15 +2237,15 @@
           <x:t xml:space="preserve">Clinician override rate</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="str"/>
-      <x:c r="C8" s="30" t="str"/>
-      <x:c r="D8" s="30" t="str"/>
-      <x:c r="E8" s="30" t="inlineStr">
+      <x:c r="B8" s="48" t="str"/>
+      <x:c r="C8" s="48" t="str"/>
+      <x:c r="D8" s="48" t="str"/>
+      <x:c r="E8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Clinical governance committee</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="30" t="str"/>
+      <x:c r="F8" s="48" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="inlineStr">
@@ -2204,15 +2253,15 @@
           <x:t xml:space="preserve">Cost per month</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="30" t="str"/>
-      <x:c r="C9" s="30" t="str"/>
-      <x:c r="D9" s="30" t="str"/>
-      <x:c r="E9" s="30" t="inlineStr">
+      <x:c r="B9" s="48" t="str"/>
+      <x:c r="C9" s="48" t="str"/>
+      <x:c r="D9" s="48" t="str"/>
+      <x:c r="E9" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Finance office</x:t>
         </x:is>
       </x:c>
-      <x:c r="F9" s="30" t="str"/>
+      <x:c r="F9" s="48" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="inlineStr">
@@ -2220,15 +2269,15 @@
           <x:t xml:space="preserve">Downtime or incidents</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="str"/>
-      <x:c r="C10" s="30" t="str"/>
-      <x:c r="D10" s="30" t="str"/>
-      <x:c r="E10" s="30" t="inlineStr">
+      <x:c r="B10" s="48" t="str"/>
+      <x:c r="C10" s="48" t="str"/>
+      <x:c r="D10" s="48" t="str"/>
+      <x:c r="E10" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">IT / cybersecurity</x:t>
         </x:is>
       </x:c>
-      <x:c r="F10" s="30" t="str"/>
+      <x:c r="F10" s="48" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="inlineStr">
@@ -2236,15 +2285,15 @@
           <x:t xml:space="preserve">Patient complaints or concerns</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="30" t="str"/>
-      <x:c r="C11" s="30" t="str"/>
-      <x:c r="D11" s="30" t="str"/>
-      <x:c r="E11" s="30" t="inlineStr">
+      <x:c r="B11" s="48" t="str"/>
+      <x:c r="C11" s="48" t="str"/>
+      <x:c r="D11" s="48" t="str"/>
+      <x:c r="E11" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Patient relations / ethics</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" s="30" t="str"/>
+      <x:c r="F11" s="48" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2264,32 +2313,32 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Indicator</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Baseline value</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="24" t="inlineStr">
+      <x:c r="C1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Current value</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" s="24" t="inlineStr">
+      <x:c r="D1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Threshold for review</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="24" t="inlineStr">
+      <x:c r="E1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Responsible role</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" s="24" t="inlineStr">
+      <x:c r="F1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Action taken</x:t>
         </x:is>
@@ -2469,12 +2518,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Field</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Description</x:t>
         </x:is>
@@ -2486,7 +2535,7 @@
           <x:t xml:space="preserve">System name</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="inlineStr">
+      <x:c r="B2" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Name and purpose of the AI system</x:t>
         </x:is>
@@ -2498,7 +2547,7 @@
           <x:t xml:space="preserve">Current version</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="inlineStr">
+      <x:c r="B3" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Version currently deployed in the hospital</x:t>
         </x:is>
@@ -2510,7 +2559,7 @@
           <x:t xml:space="preserve">Proposed version</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="inlineStr">
+      <x:c r="B4" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">New version or update proposed by vendor or internal team</x:t>
         </x:is>
@@ -2522,7 +2571,7 @@
           <x:t xml:space="preserve">Change description</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="inlineStr">
+      <x:c r="B5" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Model, data input, threshold, user interface, integration, or output changes</x:t>
         </x:is>
@@ -2534,7 +2583,7 @@
           <x:t xml:space="preserve">Reason for change</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="inlineStr">
+      <x:c r="B6" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Performance improvement, bug fix, regulatory requirement, workflow update, cost change</x:t>
         </x:is>
@@ -2546,7 +2595,7 @@
           <x:t xml:space="preserve">Validation required</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="inlineStr">
+      <x:c r="B7" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Local testing, subgroup analysis, silent-mode testing, clinical safety review</x:t>
         </x:is>
@@ -2558,7 +2607,7 @@
           <x:t xml:space="preserve">Economic effect</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="inlineStr">
+      <x:c r="B8" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Expected change in cost, workflow, avoided events, productivity, or budget impact</x:t>
         </x:is>
@@ -2570,7 +2619,7 @@
           <x:t xml:space="preserve">Equity effect</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="30" t="inlineStr">
+      <x:c r="B9" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Expected or tested effect across patient subgroups</x:t>
         </x:is>
@@ -2582,7 +2631,7 @@
           <x:t xml:space="preserve">Approval decision</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="inlineStr">
+      <x:c r="B10" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Accept, pilot, delay, reject, rollback, or retire</x:t>
         </x:is>
@@ -2594,7 +2643,7 @@
           <x:t xml:space="preserve">Communication plan</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="30" t="inlineStr">
+      <x:c r="B11" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Who must be informed and trained before implementation?</x:t>
         </x:is>
@@ -2606,7 +2655,7 @@
           <x:t xml:space="preserve">Review date</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" s="30" t="inlineStr">
+      <x:c r="B12" s="48" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Date for post-update monitoring review</x:t>
         </x:is>
@@ -2626,12 +2675,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Field</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Description</x:t>
         </x:is>
@@ -2783,12 +2832,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Question</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes / No / Evidence</x:t>
         </x:is>
@@ -2800,7 +2849,7 @@
           <x:t xml:space="preserve">Has model performance declined below an agreed threshold?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="30" t="str"/>
+      <x:c r="B2" s="48" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="inlineStr">
@@ -2808,7 +2857,7 @@
           <x:t xml:space="preserve">Has subgroup performance created equity concerns?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" s="30" t="str"/>
+      <x:c r="B3" s="48" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="17" t="inlineStr">
@@ -2816,7 +2865,7 @@
           <x:t xml:space="preserve">Have total costs exceeded the approved budget impact range?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="30" t="str"/>
+      <x:c r="B4" s="48" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="17" t="inlineStr">
@@ -2824,7 +2873,7 @@
           <x:t xml:space="preserve">Has clinician adoption fallen below a useful level?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="30" t="str"/>
+      <x:c r="B5" s="48" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17" t="inlineStr">
@@ -2832,7 +2881,7 @@
           <x:t xml:space="preserve">Has the system increased workflow burden or alert fatigue?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="30" t="str"/>
+      <x:c r="B6" s="48" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="inlineStr">
@@ -2840,7 +2889,7 @@
           <x:t xml:space="preserve">Has a privacy, cybersecurity, or continuity risk become unacceptable?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="30" t="str"/>
+      <x:c r="B7" s="48" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="inlineStr">
@@ -2848,7 +2897,7 @@
           <x:t xml:space="preserve">Has the vendor failed to meet support, monitoring, or reporting obligations?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="30" t="str"/>
+      <x:c r="B8" s="48" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="17" t="inlineStr">
@@ -2856,7 +2905,7 @@
           <x:t xml:space="preserve">Has a safer, more interoperable, or more cost-effective alternative become available?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="30" t="str"/>
+      <x:c r="B9" s="48" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="inlineStr">
@@ -2864,7 +2913,7 @@
           <x:t xml:space="preserve">Can the system be retired without disrupting patient care?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="30" t="str"/>
+      <x:c r="B10" s="48" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="inlineStr">
@@ -2872,7 +2921,7 @@
           <x:t xml:space="preserve">Has a communication and transition plan been prepared?</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="30" t="str"/>
+      <x:c r="B11" s="48" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2888,12 +2937,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="inlineStr">
+      <x:c r="A1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Question</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="24" t="inlineStr">
+      <x:c r="B1" s="47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Yes / No / Evidence</x:t>
         </x:is>
